--- a/data/RawData/data_Rouzic_2023_sexage_AIV.xlsx
+++ b/data/RawData/data_Rouzic_2023_sexage_AIV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ponchon\Documents\Projects\NorthernGannets2023\Analysis\NorthernGannets2023\data\RawData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4721E6EC-6B9F-4613-A703-A62CEBE334E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8E8267-6B9C-45BE-ADE8-228FBD76803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2903,7 +2903,7 @@
         <v>0.45069444444444445</v>
       </c>
       <c r="F10" s="20">
-        <v>233661</v>
+        <v>233661.1</v>
       </c>
       <c r="G10" s="8">
         <v>8730</v>

--- a/data/RawData/data_Rouzic_2023_sexage_AIV.xlsx
+++ b/data/RawData/data_Rouzic_2023_sexage_AIV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ponchon\Documents\Projects\NorthernGannets2023\Analysis\NorthernGannets2023\data\RawData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aponchon\Nextcloud\Aurore\Projects\NorthernGannets2023\Analysis\NorthernGannets2023\data\RawData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8E8267-6B9C-45BE-ADE8-228FBD76803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9581ECA-3C54-4972-B16E-7FE84DB65F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general_info" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="lecture_bague" sheetId="5" r:id="rId4"/>
     <sheet name="comptage" sheetId="4" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">capture_data!$A$1:$AL$48</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="306">
   <si>
     <t>species</t>
   </si>
@@ -954,6 +957,30 @@
   </si>
   <si>
     <t>AIV</t>
+  </si>
+  <si>
+    <t>Yeux_bino</t>
+  </si>
+  <si>
+    <t>Yeux_colo</t>
+  </si>
+  <si>
+    <t>1dark</t>
+  </si>
+  <si>
+    <t>1spotted</t>
+  </si>
+  <si>
+    <t>2dark</t>
+  </si>
+  <si>
+    <t>2white</t>
+  </si>
+  <si>
+    <t>2spotted</t>
+  </si>
+  <si>
+    <t>1dark1spotted</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1931,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AJ1048576"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AL1048576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1917,23 +1945,25 @@
     <col min="10" max="11" width="11" customWidth="1"/>
     <col min="13" max="13" width="16.875" style="26" customWidth="1"/>
     <col min="14" max="16" width="15.625" customWidth="1"/>
-    <col min="17" max="17" width="13.375" style="30" customWidth="1"/>
-    <col min="18" max="18" width="12.375" style="30" customWidth="1"/>
-    <col min="19" max="19" width="16.875" customWidth="1"/>
-    <col min="22" max="22" width="14.5" customWidth="1"/>
-    <col min="24" max="24" width="13.125" customWidth="1"/>
-    <col min="25" max="25" width="14.5" customWidth="1"/>
-    <col min="27" max="27" width="15.5" customWidth="1"/>
-    <col min="28" max="28" width="13.5" customWidth="1"/>
-    <col min="29" max="29" width="34.625" style="19" customWidth="1"/>
-    <col min="30" max="30" width="12.5" customWidth="1"/>
-    <col min="33" max="33" width="17.625" customWidth="1"/>
-    <col min="34" max="34" width="22" customWidth="1"/>
-    <col min="35" max="35" width="21.375" customWidth="1"/>
-    <col min="36" max="36" width="19.5" customWidth="1"/>
+    <col min="17" max="17" width="19.125" customWidth="1"/>
+    <col min="18" max="18" width="15.625" customWidth="1"/>
+    <col min="19" max="19" width="13.375" style="30" customWidth="1"/>
+    <col min="20" max="20" width="12.375" style="30" customWidth="1"/>
+    <col min="21" max="21" width="16.875" customWidth="1"/>
+    <col min="24" max="24" width="14.5" customWidth="1"/>
+    <col min="26" max="26" width="13.125" customWidth="1"/>
+    <col min="27" max="27" width="14.5" customWidth="1"/>
+    <col min="29" max="29" width="15.5" customWidth="1"/>
+    <col min="30" max="30" width="13.5" customWidth="1"/>
+    <col min="31" max="31" width="34.625" style="19" customWidth="1"/>
+    <col min="32" max="32" width="12.5" customWidth="1"/>
+    <col min="35" max="35" width="17.625" customWidth="1"/>
+    <col min="36" max="36" width="22" customWidth="1"/>
+    <col min="37" max="37" width="21.375" customWidth="1"/>
+    <col min="38" max="38" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1980,70 +2010,76 @@
         <v>26</v>
       </c>
       <c r="P1" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="R1" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="S1" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="T1" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AC1" s="23" t="s">
+      <c r="AE1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2089,58 +2125,59 @@
       <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="P2">
-        <f>IF(Q2="+",1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Q2" s="30" t="s">
+      <c r="P2" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q2">
+        <f>IF(OR(N2="dark",O2="dark",N2="spotted",O2="spotted"),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <f>IF(S2="+",1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S2" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R2" s="30" t="s">
+      <c r="T2" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>2.9</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>63.3</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>48.5</v>
       </c>
-      <c r="V2">
+      <c r="X2">
         <v>99.9</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>17</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>126</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>81</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>29</v>
       </c>
-      <c r="AA2">
+      <c r="AC2">
         <v>2</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>55</v>
       </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AE2" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>21</v>
       </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
-      <c r="AF2">
-        <v>1</v>
-      </c>
       <c r="AG2">
         <v>1</v>
       </c>
@@ -2153,8 +2190,14 @@
       <c r="AJ2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2200,49 +2243,50 @@
       <c r="O3" t="s">
         <v>28</v>
       </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P48" si="0">IF(Q3="+",1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="30" t="s">
+      <c r="P3" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q48" si="0">IF(OR(N3="dark",O3="dark",N3="spotted",O3="spotted"),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R48" si="1">IF(S3="+",1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S3" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R3" s="30" t="s">
+      <c r="T3" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>3.05</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>63.5</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>48.8</v>
       </c>
-      <c r="V3">
+      <c r="X3">
         <v>97</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>17</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" t="s">
         <v>81</v>
       </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="s">
+      <c r="AC3">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="s">
         <v>55</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AF3" t="s">
         <v>21</v>
       </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-      <c r="AF3">
-        <v>1</v>
-      </c>
       <c r="AG3">
         <v>1</v>
       </c>
@@ -2255,8 +2299,14 @@
       <c r="AJ3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2302,52 +2352,53 @@
       <c r="O4" t="s">
         <v>27</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q4" s="30" t="s">
+      <c r="R4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S4" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R4" s="30" t="s">
+      <c r="T4" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>3.25</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>66</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>50.5</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>98</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Y4" t="s">
         <v>17</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AA4" t="s">
         <v>81</v>
       </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="s">
         <v>55</v>
       </c>
-      <c r="AC4" s="19" t="s">
+      <c r="AE4" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
         <v>21</v>
       </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
-      <c r="AF4">
-        <v>1</v>
-      </c>
       <c r="AG4">
         <v>1</v>
       </c>
@@ -2360,8 +2411,14 @@
       <c r="AJ4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2407,55 +2464,56 @@
       <c r="O5" t="s">
         <v>34</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q5" s="30" t="s">
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S5" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R5" s="30" t="s">
+      <c r="T5" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>3.5</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>64.400000000000006</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>55</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>99.8</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" t="s">
         <v>17</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Z5" t="s">
         <v>126</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AA5" t="s">
         <v>81</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AB5" t="s">
         <v>35</v>
       </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="s">
         <v>55</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AF5" t="s">
         <v>21</v>
       </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
-      <c r="AF5">
-        <v>1</v>
-      </c>
       <c r="AG5">
         <v>1</v>
       </c>
@@ -2468,8 +2526,14 @@
       <c r="AJ5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2515,55 +2579,56 @@
       <c r="O6" t="s">
         <v>27</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="30" t="s">
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S6" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R6" s="30" t="s">
+      <c r="T6" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>2.75</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>67.7</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>49.3</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>102.9</v>
       </c>
-      <c r="W6" t="s">
+      <c r="Y6" t="s">
         <v>17</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Z6" t="s">
         <v>126</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AA6" t="s">
         <v>81</v>
       </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="s">
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="s">
         <v>55</v>
       </c>
-      <c r="AC6" s="19" t="s">
+      <c r="AE6" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AF6" t="s">
         <v>21</v>
       </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6">
-        <v>1</v>
-      </c>
       <c r="AG6">
         <v>1</v>
       </c>
@@ -2576,8 +2641,14 @@
       <c r="AJ6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2623,49 +2694,50 @@
       <c r="O7" t="s">
         <v>27</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="30" t="s">
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R7" s="30" t="s">
+      <c r="T7" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>3.15</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>69</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>49.1</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>96</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
         <v>17</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AA7" t="s">
         <v>81</v>
       </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="s">
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="s">
         <v>55</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AF7" t="s">
         <v>21</v>
       </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
-      <c r="AF7">
-        <v>1</v>
-      </c>
       <c r="AG7">
         <v>1</v>
       </c>
@@ -2678,8 +2750,14 @@
       <c r="AJ7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2725,52 +2803,53 @@
       <c r="O8" t="s">
         <v>28</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="30" t="s">
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R8" s="30" t="s">
+      <c r="T8" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>3.15</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>65</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>49.7</v>
       </c>
-      <c r="V8">
+      <c r="X8">
         <v>100</v>
       </c>
-      <c r="W8" t="s">
+      <c r="Y8" t="s">
         <v>17</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AA8" t="s">
         <v>81</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AB8" t="s">
         <v>63</v>
       </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="s">
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="s">
         <v>55</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AF8" t="s">
         <v>21</v>
       </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-      <c r="AF8">
-        <v>1</v>
-      </c>
       <c r="AG8">
         <v>1</v>
       </c>
@@ -2783,8 +2862,14 @@
       <c r="AJ8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2830,49 +2915,50 @@
       <c r="O9" t="s">
         <v>28</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="T9" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>2.8</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>63</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>49.5</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>103.2</v>
       </c>
-      <c r="W9" t="s">
+      <c r="Y9" t="s">
         <v>17</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="AA9" t="s">
         <v>81</v>
       </c>
-      <c r="AA9">
+      <c r="AC9">
         <v>2</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AD9" t="s">
         <v>55</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AF9" t="s">
         <v>21</v>
       </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-      <c r="AF9">
-        <v>1</v>
-      </c>
       <c r="AG9">
         <v>1</v>
       </c>
@@ -2885,8 +2971,14 @@
       <c r="AJ9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:36" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2932,55 +3024,56 @@
       <c r="O10" t="s">
         <v>28</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q10" s="30" t="s">
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S10" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R10" s="30" t="s">
+      <c r="T10" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>3.2</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>57.4</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>50</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>98.8</v>
       </c>
-      <c r="W10" t="s">
+      <c r="Y10" t="s">
         <v>17</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="AA10" t="s">
         <v>81</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AB10" t="s">
         <v>35</v>
       </c>
-      <c r="AA10">
+      <c r="AC10">
         <v>2</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AD10" t="s">
         <v>55</v>
       </c>
-      <c r="AC10" s="21" t="s">
+      <c r="AE10" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AF10" t="s">
         <v>21</v>
       </c>
-      <c r="AE10">
-        <v>1</v>
-      </c>
-      <c r="AF10">
-        <v>1</v>
-      </c>
       <c r="AG10">
         <v>1</v>
       </c>
@@ -2993,8 +3086,14 @@
       <c r="AJ10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3040,52 +3139,53 @@
       <c r="O11" t="s">
         <v>27</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="30" t="s">
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R11" s="30" t="s">
+      <c r="T11" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>3.5</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>64.900000000000006</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>49.8</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>101.3</v>
       </c>
-      <c r="W11" t="s">
+      <c r="Y11" t="s">
         <v>17</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="AA11" t="s">
         <v>81</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AB11" t="s">
         <v>35</v>
       </c>
-      <c r="AA11">
+      <c r="AC11">
         <v>2</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AD11" t="s">
         <v>55</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AF11" t="s">
         <v>21</v>
       </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-      <c r="AF11">
-        <v>1</v>
-      </c>
       <c r="AG11">
         <v>1</v>
       </c>
@@ -3098,8 +3198,14 @@
       <c r="AJ11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -3145,49 +3251,50 @@
       <c r="O12" t="s">
         <v>27</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="30" t="s">
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R12" s="30" t="s">
+      <c r="T12" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>3.3</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>61.9</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>50.6</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>99.3</v>
       </c>
-      <c r="W12" t="s">
+      <c r="Y12" t="s">
         <v>17</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="AA12" t="s">
         <v>81</v>
       </c>
-      <c r="AA12">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="s">
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AF12" t="s">
         <v>21</v>
       </c>
-      <c r="AE12">
-        <v>1</v>
-      </c>
-      <c r="AF12">
-        <v>1</v>
-      </c>
       <c r="AG12">
         <v>1</v>
       </c>
@@ -3200,8 +3307,14 @@
       <c r="AJ12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3247,49 +3360,50 @@
       <c r="O13" t="s">
         <v>27</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="30" t="s">
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R13" s="30" t="s">
+      <c r="T13" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>3.15</v>
       </c>
-      <c r="T13">
+      <c r="V13">
         <v>64.400000000000006</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>49</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>97.3</v>
       </c>
-      <c r="W13" t="s">
+      <c r="Y13" t="s">
         <v>17</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="AA13" t="s">
         <v>81</v>
       </c>
-      <c r="AA13">
+      <c r="AC13">
         <v>2</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AD13" t="s">
         <v>55</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AF13" t="s">
         <v>21</v>
       </c>
-      <c r="AE13">
-        <v>1</v>
-      </c>
-      <c r="AF13">
-        <v>1</v>
-      </c>
       <c r="AG13">
         <v>1</v>
       </c>
@@ -3302,8 +3416,14 @@
       <c r="AJ13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK13">
+        <v>1</v>
+      </c>
+      <c r="AL13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3349,49 +3469,50 @@
       <c r="O14" t="s">
         <v>27</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="30" t="s">
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R14" s="30" t="s">
+      <c r="T14" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>3.2</v>
       </c>
-      <c r="T14">
+      <c r="V14">
         <v>60.9</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>50.2</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>96.3</v>
       </c>
-      <c r="W14" t="s">
+      <c r="Y14" t="s">
         <v>17</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="AA14" t="s">
         <v>81</v>
       </c>
-      <c r="AA14">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="s">
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="s">
         <v>55</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AF14" t="s">
         <v>21</v>
       </c>
-      <c r="AE14">
-        <v>1</v>
-      </c>
-      <c r="AF14">
-        <v>1</v>
-      </c>
       <c r="AG14">
         <v>1</v>
       </c>
@@ -3404,8 +3525,14 @@
       <c r="AJ14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK14">
+        <v>1</v>
+      </c>
+      <c r="AL14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -3451,49 +3578,50 @@
       <c r="O15" t="s">
         <v>27</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="30" t="s">
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R15" s="30" t="s">
+      <c r="T15" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>3</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>64.5</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>49.3</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>107.4</v>
       </c>
-      <c r="W15" t="s">
+      <c r="Y15" t="s">
         <v>17</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="AA15" t="s">
         <v>81</v>
       </c>
-      <c r="AA15">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="s">
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="s">
         <v>55</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AF15" t="s">
         <v>21</v>
       </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
       <c r="AG15">
         <v>1</v>
       </c>
@@ -3506,8 +3634,14 @@
       <c r="AJ15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -3553,52 +3687,53 @@
       <c r="O16" t="s">
         <v>27</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="30" t="s">
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R16" s="30" t="s">
+      <c r="T16" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>3.15</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>82.1</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>48.6</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>93</v>
       </c>
-      <c r="W16" t="s">
+      <c r="Y16" t="s">
         <v>17</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="AA16" t="s">
         <v>81</v>
       </c>
-      <c r="AA16">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="s">
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="s">
         <v>55</v>
       </c>
-      <c r="AC16" s="19" t="s">
+      <c r="AE16" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AF16" t="s">
         <v>21</v>
       </c>
-      <c r="AE16">
-        <v>1</v>
-      </c>
-      <c r="AF16">
-        <v>1</v>
-      </c>
       <c r="AG16">
         <v>1</v>
       </c>
@@ -3611,8 +3746,14 @@
       <c r="AJ16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -3658,52 +3799,53 @@
       <c r="O17" t="s">
         <v>27</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="30" t="s">
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R17" s="30" t="s">
+      <c r="T17" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>2.65</v>
       </c>
-      <c r="T17">
+      <c r="V17">
         <v>62.6</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>48.3</v>
       </c>
-      <c r="V17">
+      <c r="X17">
         <v>97.9</v>
       </c>
-      <c r="W17" t="s">
+      <c r="Y17" t="s">
         <v>17</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AA17" t="s">
         <v>81</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AB17" t="s">
         <v>52</v>
       </c>
-      <c r="AA17">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="s">
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="s">
         <v>55</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AF17" t="s">
         <v>21</v>
       </c>
-      <c r="AE17">
-        <v>1</v>
-      </c>
-      <c r="AF17">
-        <v>1</v>
-      </c>
       <c r="AG17">
         <v>1</v>
       </c>
@@ -3716,8 +3858,14 @@
       <c r="AJ17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK17">
+        <v>1</v>
+      </c>
+      <c r="AL17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -3763,52 +3911,53 @@
       <c r="O18" t="s">
         <v>27</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="30" t="s">
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R18" s="30" t="s">
+      <c r="T18" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>3</v>
       </c>
-      <c r="T18">
+      <c r="V18">
         <v>62.2</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>48.7</v>
       </c>
-      <c r="V18">
+      <c r="X18">
         <v>99.6</v>
       </c>
-      <c r="W18" t="s">
+      <c r="Y18" t="s">
         <v>17</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="AA18" t="s">
         <v>82</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AB18" t="s">
         <v>52</v>
       </c>
-      <c r="AA18">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="s">
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="s">
         <v>55</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AF18" t="s">
         <v>21</v>
       </c>
-      <c r="AE18">
-        <v>1</v>
-      </c>
-      <c r="AF18">
-        <v>1</v>
-      </c>
       <c r="AG18">
         <v>1</v>
       </c>
@@ -3821,8 +3970,14 @@
       <c r="AJ18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK18">
+        <v>1</v>
+      </c>
+      <c r="AL18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -3868,52 +4023,53 @@
       <c r="O19" t="s">
         <v>27</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="30" t="s">
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R19" s="30" t="s">
+      <c r="T19" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>3.25</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>62.7</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>50.2</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>105</v>
       </c>
-      <c r="W19" t="s">
+      <c r="Y19" t="s">
         <v>17</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="AA19" t="s">
         <v>82</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AB19" t="s">
         <v>35</v>
       </c>
-      <c r="AA19">
+      <c r="AC19">
         <v>2</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AD19" t="s">
         <v>55</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AF19" t="s">
         <v>21</v>
       </c>
-      <c r="AE19">
-        <v>1</v>
-      </c>
-      <c r="AF19">
-        <v>1</v>
-      </c>
       <c r="AG19">
         <v>1</v>
       </c>
@@ -3926,8 +4082,14 @@
       <c r="AJ19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AL19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -3973,49 +4135,50 @@
       <c r="O20" t="s">
         <v>27</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="30" t="s">
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R20" s="30" t="s">
+      <c r="T20" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>2.95</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>63.7</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>49.2</v>
       </c>
-      <c r="V20">
+      <c r="X20">
         <v>102.1</v>
       </c>
-      <c r="W20" t="s">
+      <c r="Y20" t="s">
         <v>17</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="AA20" t="s">
         <v>82</v>
       </c>
-      <c r="AA20">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="s">
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="s">
         <v>55</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AF20" t="s">
         <v>21</v>
       </c>
-      <c r="AE20">
-        <v>1</v>
-      </c>
-      <c r="AF20">
-        <v>1</v>
-      </c>
       <c r="AG20">
         <v>1</v>
       </c>
@@ -4028,8 +4191,14 @@
       <c r="AJ20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK20">
+        <v>1</v>
+      </c>
+      <c r="AL20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -4075,49 +4244,50 @@
       <c r="O21" t="s">
         <v>27</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="30" t="s">
+      <c r="R21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R21" s="30" t="s">
+      <c r="T21" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>2.9</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>64.5</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>49.1</v>
       </c>
-      <c r="V21" s="14" t="s">
+      <c r="X21" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="W21" t="s">
+      <c r="Y21" t="s">
         <v>17</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="AA21" t="s">
         <v>82</v>
       </c>
-      <c r="AA21">
+      <c r="AC21">
         <v>3</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AD21" t="s">
         <v>55</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AF21" t="s">
         <v>21</v>
       </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AF21">
-        <v>1</v>
-      </c>
       <c r="AG21">
         <v>1</v>
       </c>
@@ -4130,8 +4300,14 @@
       <c r="AJ21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK21">
+        <v>1</v>
+      </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -4177,63 +4353,70 @@
       <c r="O22" t="s">
         <v>27</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="30" t="s">
+      <c r="R22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R22" s="30" t="s">
+      <c r="T22" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>2.5499999999999998</v>
       </c>
-      <c r="T22">
+      <c r="V22">
         <v>59.9</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>49.2</v>
       </c>
-      <c r="V22">
+      <c r="X22">
         <v>91.4</v>
       </c>
-      <c r="W22" t="s">
+      <c r="Y22" t="s">
         <v>17</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AA22" t="s">
         <v>82</v>
       </c>
-      <c r="AA22">
+      <c r="AC22">
         <v>2</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AD22" t="s">
         <v>55</v>
       </c>
-      <c r="AD22" t="s">
+      <c r="AF22" t="s">
         <v>21</v>
       </c>
-      <c r="AE22">
-        <v>1</v>
-      </c>
-      <c r="AF22">
-        <v>1</v>
-      </c>
       <c r="AG22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
+        <v>1</v>
+      </c>
+      <c r="AI22">
         <v>0</v>
       </c>
-      <c r="AH22">
-        <v>1</v>
-      </c>
-      <c r="AI22">
-        <v>1</v>
-      </c>
       <c r="AJ22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK22">
+        <v>1</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -4279,63 +4462,70 @@
       <c r="O23" t="s">
         <v>27</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q23">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q23" s="30" t="s">
+      <c r="R23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S23" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R23" s="30" t="s">
+      <c r="T23" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>2.9</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>59.7</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>49</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>95.2</v>
       </c>
-      <c r="W23" t="s">
+      <c r="Y23" t="s">
         <v>17</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="AA23" t="s">
         <v>82</v>
       </c>
-      <c r="AA23">
+      <c r="AC23">
         <v>2</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AD23" t="s">
         <v>55</v>
       </c>
-      <c r="AD23" t="s">
+      <c r="AF23" t="s">
         <v>21</v>
       </c>
-      <c r="AE23">
-        <v>1</v>
-      </c>
-      <c r="AF23">
-        <v>1</v>
-      </c>
       <c r="AG23">
+        <v>1</v>
+      </c>
+      <c r="AH23">
+        <v>1</v>
+      </c>
+      <c r="AI23">
         <v>0</v>
       </c>
-      <c r="AH23">
-        <v>1</v>
-      </c>
-      <c r="AI23">
-        <v>1</v>
-      </c>
       <c r="AJ23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK23">
+        <v>1</v>
+      </c>
+      <c r="AL23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -4381,63 +4571,70 @@
       <c r="O24" t="s">
         <v>27</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q24" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S24" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R24" s="30" t="s">
+      <c r="T24" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>3.45</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>61.5</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>51</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>106.8</v>
       </c>
-      <c r="W24" t="s">
+      <c r="Y24" t="s">
         <v>17</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AA24" t="s">
         <v>82</v>
       </c>
-      <c r="AA24">
-        <v>1</v>
-      </c>
-      <c r="AB24" t="s">
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="s">
         <v>55</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AF24" t="s">
         <v>21</v>
       </c>
-      <c r="AE24">
-        <v>1</v>
-      </c>
-      <c r="AF24">
-        <v>1</v>
-      </c>
       <c r="AG24">
+        <v>1</v>
+      </c>
+      <c r="AH24">
+        <v>1</v>
+      </c>
+      <c r="AI24">
         <v>0</v>
       </c>
-      <c r="AH24">
-        <v>1</v>
-      </c>
-      <c r="AI24">
-        <v>1</v>
-      </c>
       <c r="AJ24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK24">
+        <v>1</v>
+      </c>
+      <c r="AL24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -4483,63 +4680,70 @@
       <c r="O25" t="s">
         <v>27</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="30" t="s">
+      <c r="R25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R25" s="30" t="s">
+      <c r="T25" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>3.25</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>59.4</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>49.1</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>100.7</v>
       </c>
-      <c r="W25" t="s">
+      <c r="Y25" t="s">
         <v>17</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="AA25" t="s">
         <v>82</v>
       </c>
-      <c r="AA25">
+      <c r="AC25">
         <v>2</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AD25" t="s">
         <v>55</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AF25" t="s">
         <v>21</v>
       </c>
-      <c r="AE25">
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <v>1</v>
-      </c>
       <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>1</v>
+      </c>
+      <c r="AI25">
         <v>0</v>
       </c>
-      <c r="AH25">
-        <v>1</v>
-      </c>
-      <c r="AI25">
-        <v>1</v>
-      </c>
       <c r="AJ25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK25">
+        <v>1</v>
+      </c>
+      <c r="AL25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -4585,66 +4789,73 @@
       <c r="O26" t="s">
         <v>27</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="30" t="s">
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R26" s="30" t="s">
+      <c r="T26" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>3.15</v>
       </c>
-      <c r="T26">
+      <c r="V26">
         <v>59.7</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>49.3</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>103.4</v>
       </c>
-      <c r="W26" t="s">
+      <c r="Y26" t="s">
         <v>17</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AA26" t="s">
         <v>82</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AB26" t="s">
         <v>35</v>
       </c>
-      <c r="AA26">
+      <c r="AC26">
         <v>2</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AD26" t="s">
         <v>55</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AF26" t="s">
         <v>21</v>
       </c>
-      <c r="AE26">
-        <v>1</v>
-      </c>
-      <c r="AF26">
-        <v>1</v>
-      </c>
       <c r="AG26">
+        <v>1</v>
+      </c>
+      <c r="AH26">
+        <v>1</v>
+      </c>
+      <c r="AI26">
         <v>0</v>
       </c>
-      <c r="AH26">
-        <v>1</v>
-      </c>
-      <c r="AI26">
-        <v>1</v>
-      </c>
       <c r="AJ26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK26">
+        <v>1</v>
+      </c>
+      <c r="AL26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -4690,66 +4901,73 @@
       <c r="O27" t="s">
         <v>34</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q27">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q27" s="30" t="s">
+      <c r="R27">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S27" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R27" s="30" t="s">
+      <c r="T27" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>2.65</v>
       </c>
-      <c r="T27">
+      <c r="V27">
         <v>57.9</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>48</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>99.3</v>
       </c>
-      <c r="W27" t="s">
+      <c r="Y27" t="s">
         <v>17</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Z27" t="s">
         <v>126</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="AA27" t="s">
         <v>82</v>
       </c>
-      <c r="AA27">
+      <c r="AC27">
         <v>2</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AD27" t="s">
         <v>55</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AF27" t="s">
         <v>21</v>
       </c>
-      <c r="AE27">
-        <v>1</v>
-      </c>
-      <c r="AF27">
-        <v>1</v>
-      </c>
       <c r="AG27">
+        <v>1</v>
+      </c>
+      <c r="AH27">
+        <v>1</v>
+      </c>
+      <c r="AI27">
         <v>0</v>
       </c>
-      <c r="AH27">
-        <v>1</v>
-      </c>
-      <c r="AI27">
-        <v>1</v>
-      </c>
       <c r="AJ27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK27">
+        <v>1</v>
+      </c>
+      <c r="AL27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -4795,66 +5013,73 @@
       <c r="O28" t="s">
         <v>27</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q28">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q28" s="30" t="s">
+      <c r="R28">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S28" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R28" s="30" t="s">
+      <c r="T28" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>3.3</v>
       </c>
-      <c r="T28">
+      <c r="V28">
         <v>61.2</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>50</v>
       </c>
-      <c r="V28">
+      <c r="X28">
         <v>101.2</v>
       </c>
-      <c r="W28" t="s">
+      <c r="Y28" t="s">
         <v>17</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="AA28" t="s">
         <v>82</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AB28" t="s">
         <v>52</v>
       </c>
-      <c r="AA28">
+      <c r="AC28">
         <v>2</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AD28" t="s">
         <v>55</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AF28" t="s">
         <v>21</v>
       </c>
-      <c r="AE28">
-        <v>1</v>
-      </c>
-      <c r="AF28">
-        <v>1</v>
-      </c>
       <c r="AG28">
+        <v>1</v>
+      </c>
+      <c r="AH28">
+        <v>1</v>
+      </c>
+      <c r="AI28">
         <v>0</v>
       </c>
-      <c r="AH28">
-        <v>1</v>
-      </c>
-      <c r="AI28">
-        <v>1</v>
-      </c>
       <c r="AJ28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK28">
+        <v>1</v>
+      </c>
+      <c r="AL28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -4897,1796 +5122,1850 @@
       <c r="O29" t="s">
         <v>194</v>
       </c>
-      <c r="P29">
+      <c r="R29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T29" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U29">
+        <v>3.7</v>
+      </c>
+      <c r="V29">
+        <v>65.8</v>
+      </c>
+      <c r="W29">
+        <v>41.1</v>
+      </c>
+      <c r="X29">
+        <v>93.2</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC29">
+        <v>2</v>
+      </c>
+      <c r="AE29" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG29">
+        <v>1</v>
+      </c>
+      <c r="AH29">
+        <v>1</v>
+      </c>
+      <c r="AI29">
+        <v>1</v>
+      </c>
+      <c r="AJ29">
+        <v>1</v>
+      </c>
+      <c r="AK29">
+        <v>1</v>
+      </c>
+      <c r="AL29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="4">
+        <v>45160</v>
+      </c>
+      <c r="D30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.73125000000000007</v>
+      </c>
+      <c r="F30" s="8">
+        <v>235188</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="8">
+        <v>53102</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N30" t="s">
+        <v>194</v>
+      </c>
+      <c r="O30" t="s">
+        <v>194</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T30" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U30">
+        <v>3.1</v>
+      </c>
+      <c r="V30">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="W30">
+        <v>37.9</v>
+      </c>
+      <c r="X30">
+        <v>95.3</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG30">
+        <v>1</v>
+      </c>
+      <c r="AH30">
+        <v>1</v>
+      </c>
+      <c r="AI30">
+        <v>1</v>
+      </c>
+      <c r="AJ30">
+        <v>1</v>
+      </c>
+      <c r="AK30">
+        <v>1</v>
+      </c>
+      <c r="AL30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="4">
+        <v>45160</v>
+      </c>
+      <c r="D31" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="F31" s="8">
+        <v>235189</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="8">
+        <v>53103</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" t="s">
+        <v>194</v>
+      </c>
+      <c r="O31" t="s">
+        <v>194</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T31" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U31">
+        <v>3.3</v>
+      </c>
+      <c r="V31">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="W31">
+        <v>38</v>
+      </c>
+      <c r="X31">
+        <v>93.2</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="24"/>
+      <c r="AF31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG31">
+        <v>1</v>
+      </c>
+      <c r="AH31">
+        <v>1</v>
+      </c>
+      <c r="AI31">
+        <v>1</v>
+      </c>
+      <c r="AJ31">
+        <v>1</v>
+      </c>
+      <c r="AK31">
+        <v>1</v>
+      </c>
+      <c r="AL31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="4">
+        <v>45160</v>
+      </c>
+      <c r="D32" t="s">
+        <v>187</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0.81527777777777777</v>
+      </c>
+      <c r="F32" s="8">
+        <v>235190</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="8">
+        <v>53104</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N32" t="s">
+        <v>194</v>
+      </c>
+      <c r="O32" t="s">
+        <v>194</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T32" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U32">
+        <v>3.35</v>
+      </c>
+      <c r="V32">
+        <v>63.9</v>
+      </c>
+      <c r="W32">
+        <v>42.3</v>
+      </c>
+      <c r="X32">
+        <v>98</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG32">
+        <v>1</v>
+      </c>
+      <c r="AH32">
+        <v>1</v>
+      </c>
+      <c r="AI32">
+        <v>1</v>
+      </c>
+      <c r="AJ32">
+        <v>1</v>
+      </c>
+      <c r="AK32">
+        <v>1</v>
+      </c>
+      <c r="AL32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="4">
+        <v>45160</v>
+      </c>
+      <c r="D33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.84930555555555554</v>
+      </c>
+      <c r="F33" s="8">
+        <v>235191</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I33" s="8">
+        <v>53105</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" t="s">
+        <v>194</v>
+      </c>
+      <c r="O33" t="s">
+        <v>194</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T33" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U33">
+        <v>3.45</v>
+      </c>
+      <c r="V33">
+        <v>63.1</v>
+      </c>
+      <c r="W33">
+        <v>39.4</v>
+      </c>
+      <c r="X33">
+        <v>97.7</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG33">
+        <v>1</v>
+      </c>
+      <c r="AH33">
+        <v>1</v>
+      </c>
+      <c r="AI33">
+        <v>1</v>
+      </c>
+      <c r="AJ33">
+        <v>1</v>
+      </c>
+      <c r="AK33">
+        <v>1</v>
+      </c>
+      <c r="AL33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="4">
+        <v>45160</v>
+      </c>
+      <c r="D34" t="s">
+        <v>189</v>
+      </c>
+      <c r="E34" s="5">
+        <v>0.89027777777777783</v>
+      </c>
+      <c r="F34" s="8">
+        <v>235192</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34" s="8">
+        <v>53106</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N34" t="s">
+        <v>194</v>
+      </c>
+      <c r="O34" t="s">
+        <v>194</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T34" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U34">
+        <v>3.35</v>
+      </c>
+      <c r="V34">
+        <v>66.8</v>
+      </c>
+      <c r="W34">
+        <v>42.5</v>
+      </c>
+      <c r="X34">
+        <v>95.9</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG34">
+        <v>1</v>
+      </c>
+      <c r="AH34">
+        <v>1</v>
+      </c>
+      <c r="AI34">
+        <v>1</v>
+      </c>
+      <c r="AJ34">
+        <v>1</v>
+      </c>
+      <c r="AK34">
+        <v>1</v>
+      </c>
+      <c r="AL34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.38472222222222219</v>
+      </c>
+      <c r="F35" s="8">
+        <v>235193</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" s="8">
+        <v>53107</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="P35" s="8"/>
+      <c r="R35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T35" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U35">
+        <v>3.7</v>
+      </c>
+      <c r="V35">
+        <v>66.3</v>
+      </c>
+      <c r="W35">
+        <v>44.3</v>
+      </c>
+      <c r="X35">
+        <v>99.3</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC35">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG35">
+        <v>1</v>
+      </c>
+      <c r="AH35">
+        <v>1</v>
+      </c>
+      <c r="AI35">
+        <v>1</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>1</v>
+      </c>
+      <c r="AL35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D36" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="F36" s="8">
+        <v>235194</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I36" s="8">
+        <v>53108</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="P36" s="8"/>
+      <c r="R36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T36" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U36">
+        <v>3.25</v>
+      </c>
+      <c r="V36">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="W36">
+        <v>44.1</v>
+      </c>
+      <c r="X36">
+        <v>100.1</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC36">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG36">
+        <v>1</v>
+      </c>
+      <c r="AH36">
+        <v>1</v>
+      </c>
+      <c r="AI36">
+        <v>1</v>
+      </c>
+      <c r="AJ36">
+        <v>1</v>
+      </c>
+      <c r="AK36">
+        <v>1</v>
+      </c>
+      <c r="AL36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="F37" s="8">
+        <v>235195</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I37" s="8">
+        <v>53109</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="30" t="s">
+      <c r="R37">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S37" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="T37" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="U37">
+        <v>3.35</v>
+      </c>
+      <c r="V37">
+        <v>66.7</v>
+      </c>
+      <c r="W37">
+        <v>49.6</v>
+      </c>
+      <c r="X37">
+        <v>99.9</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AE37" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG37">
+        <v>1</v>
+      </c>
+      <c r="AH37">
+        <v>1</v>
+      </c>
+      <c r="AI37">
+        <v>1</v>
+      </c>
+      <c r="AJ37">
+        <v>1</v>
+      </c>
+      <c r="AK37">
+        <v>1</v>
+      </c>
+      <c r="AL37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D38" t="s">
+        <v>205</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="F38" s="8">
+        <v>235196</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I38" s="8">
+        <v>53110</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="P38" s="8"/>
+      <c r="R38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R29" s="30" t="s">
+      <c r="T38" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S29">
-        <v>3.7</v>
-      </c>
-      <c r="T29">
-        <v>65.8</v>
-      </c>
-      <c r="U29">
-        <v>41.1</v>
-      </c>
-      <c r="V29">
-        <v>93.2</v>
-      </c>
-      <c r="W29" t="s">
+      <c r="U38">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V38">
+        <v>63.6</v>
+      </c>
+      <c r="W38">
+        <v>41.7</v>
+      </c>
+      <c r="X38">
+        <v>98.1</v>
+      </c>
+      <c r="Y38" t="s">
         <v>17</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Z38" t="s">
         <v>126</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="AA38" t="s">
         <v>195</v>
       </c>
-      <c r="Z29" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA29">
-        <v>2</v>
-      </c>
-      <c r="AC29" s="25" t="s">
-        <v>277</v>
-      </c>
-      <c r="AD29" t="s">
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="AF38" t="s">
         <v>21</v>
       </c>
-      <c r="AE29">
-        <v>1</v>
-      </c>
-      <c r="AF29">
-        <v>1</v>
-      </c>
-      <c r="AG29">
-        <v>1</v>
-      </c>
-      <c r="AH29">
-        <v>1</v>
-      </c>
-      <c r="AI29">
-        <v>1</v>
-      </c>
-      <c r="AJ29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="AG38">
+        <v>1</v>
+      </c>
+      <c r="AH38">
+        <v>1</v>
+      </c>
+      <c r="AI38">
+        <v>1</v>
+      </c>
+      <c r="AJ38">
+        <v>1</v>
+      </c>
+      <c r="AK38">
+        <v>1</v>
+      </c>
+      <c r="AL38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>12</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B39" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="4">
-        <v>45160</v>
-      </c>
-      <c r="D30" t="s">
-        <v>185</v>
-      </c>
-      <c r="E30" s="5">
-        <v>0.73125000000000007</v>
-      </c>
-      <c r="F30" s="8">
-        <v>235188</v>
-      </c>
-      <c r="G30" s="8" t="s">
+      <c r="C39" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D39" t="s">
+        <v>206</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="F39" s="8">
+        <v>235197</v>
+      </c>
+      <c r="G39" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H39" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I30" s="8">
-        <v>53102</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L30" s="8" t="s">
+      <c r="I39" s="8">
+        <v>53111</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="N30" t="s">
-        <v>194</v>
-      </c>
-      <c r="O30" t="s">
-        <v>194</v>
-      </c>
-      <c r="P30">
+      <c r="M39" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="30" t="s">
+      <c r="R39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R30" s="30" t="s">
+      <c r="T39" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S30">
-        <v>3.1</v>
-      </c>
-      <c r="T30">
-        <v>64.400000000000006</v>
-      </c>
-      <c r="U30">
-        <v>37.9</v>
-      </c>
-      <c r="V30">
-        <v>95.3</v>
-      </c>
-      <c r="W30" t="s">
+      <c r="U39">
+        <v>2.95</v>
+      </c>
+      <c r="V39">
+        <v>62.9</v>
+      </c>
+      <c r="W39">
+        <v>49.4</v>
+      </c>
+      <c r="X39">
+        <v>100</v>
+      </c>
+      <c r="Y39" t="s">
         <v>17</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Z39" t="s">
         <v>126</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="AA39" t="s">
         <v>195</v>
       </c>
-      <c r="AA30">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="AD30" t="s">
+      <c r="AC39">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG39">
+        <v>1</v>
+      </c>
+      <c r="AH39">
+        <v>1</v>
+      </c>
+      <c r="AI39">
+        <v>1</v>
+      </c>
+      <c r="AJ39">
+        <v>1</v>
+      </c>
+      <c r="AK39">
+        <v>1</v>
+      </c>
+      <c r="AL39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E40" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F40" s="8">
+        <v>235198</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I40" s="8">
+        <v>53112</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="P40" s="8"/>
+      <c r="R40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="T40" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="U40">
+        <v>3.55</v>
+      </c>
+      <c r="V40">
+        <v>66.8</v>
+      </c>
+      <c r="W40">
+        <v>43.6</v>
+      </c>
+      <c r="X40">
+        <v>97.2</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC40">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="AF40" t="s">
         <v>21</v>
       </c>
-      <c r="AE30">
-        <v>1</v>
-      </c>
-      <c r="AF30">
-        <v>1</v>
-      </c>
-      <c r="AG30">
-        <v>1</v>
-      </c>
-      <c r="AH30">
-        <v>1</v>
-      </c>
-      <c r="AI30">
-        <v>1</v>
-      </c>
-      <c r="AJ30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="AG40">
+        <v>1</v>
+      </c>
+      <c r="AH40">
+        <v>1</v>
+      </c>
+      <c r="AI40">
+        <v>1</v>
+      </c>
+      <c r="AJ40">
+        <v>1</v>
+      </c>
+      <c r="AK40">
+        <v>1</v>
+      </c>
+      <c r="AL40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>12</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B41" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="4">
-        <v>45160</v>
-      </c>
-      <c r="D31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="F31" s="8">
-        <v>235189</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="C41" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D41" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0.68194444444444446</v>
+      </c>
+      <c r="F41" s="8">
+        <v>235199</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H41" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I31" s="8">
-        <v>53103</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L31" s="8" t="s">
+      <c r="I41" s="8">
+        <v>53113</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S41" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="T41" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="U41">
+        <v>2.6</v>
+      </c>
+      <c r="V41">
+        <v>63.2</v>
+      </c>
+      <c r="W41">
+        <v>50.3</v>
+      </c>
+      <c r="X41">
+        <v>100.4</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG41">
+        <v>1</v>
+      </c>
+      <c r="AH41">
+        <v>1</v>
+      </c>
+      <c r="AI41">
+        <v>1</v>
+      </c>
+      <c r="AJ41">
+        <v>1</v>
+      </c>
+      <c r="AK41">
+        <v>1</v>
+      </c>
+      <c r="AL41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D42" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" s="5">
+        <v>0.78125</v>
+      </c>
+      <c r="F42" s="8">
+        <v>235200</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I42" s="8">
+        <v>53114</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="N31" t="s">
-        <v>194</v>
-      </c>
-      <c r="O31" t="s">
-        <v>194</v>
-      </c>
-      <c r="P31">
+      <c r="M42" s="26">
+        <v>6</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O42" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S42" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="T42" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="U42">
+        <v>3.4</v>
+      </c>
+      <c r="V42">
+        <v>64.8</v>
+      </c>
+      <c r="W42">
+        <v>50.4</v>
+      </c>
+      <c r="X42">
+        <v>98.1</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC42">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG42">
+        <v>1</v>
+      </c>
+      <c r="AH42">
+        <v>1</v>
+      </c>
+      <c r="AI42">
+        <v>1</v>
+      </c>
+      <c r="AJ42">
+        <v>1</v>
+      </c>
+      <c r="AK42">
+        <v>1</v>
+      </c>
+      <c r="AL42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="F43" s="8">
+        <v>235201</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I43" s="8">
+        <v>53115</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="30" t="s">
+      <c r="R43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R31" s="30" t="s">
+      <c r="T43" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S31">
-        <v>3.3</v>
-      </c>
-      <c r="T31">
-        <v>64.400000000000006</v>
-      </c>
-      <c r="U31">
-        <v>38</v>
-      </c>
-      <c r="V31">
-        <v>93.2</v>
-      </c>
-      <c r="W31" t="s">
+      <c r="U43">
+        <v>2.8</v>
+      </c>
+      <c r="V43">
+        <v>64.7</v>
+      </c>
+      <c r="W43">
+        <v>50.2</v>
+      </c>
+      <c r="X43">
+        <v>100.5</v>
+      </c>
+      <c r="Y43" t="s">
         <v>17</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Z43" t="s">
         <v>126</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="AA43" t="s">
         <v>195</v>
       </c>
-      <c r="AA31">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="24"/>
-      <c r="AD31" t="s">
+      <c r="AC43">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF43" t="s">
         <v>21</v>
       </c>
-      <c r="AE31">
-        <v>1</v>
-      </c>
-      <c r="AF31">
-        <v>1</v>
-      </c>
-      <c r="AG31">
-        <v>1</v>
-      </c>
-      <c r="AH31">
-        <v>1</v>
-      </c>
-      <c r="AI31">
-        <v>1</v>
-      </c>
-      <c r="AJ31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="AG43">
+        <v>1</v>
+      </c>
+      <c r="AH43">
+        <v>1</v>
+      </c>
+      <c r="AI43">
+        <v>1</v>
+      </c>
+      <c r="AJ43">
+        <v>1</v>
+      </c>
+      <c r="AK43">
+        <v>1</v>
+      </c>
+      <c r="AL43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>12</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="4">
-        <v>45160</v>
-      </c>
-      <c r="D32" t="s">
-        <v>187</v>
-      </c>
-      <c r="E32" s="5">
-        <v>0.81527777777777777</v>
-      </c>
-      <c r="F32" s="8">
-        <v>235190</v>
-      </c>
-      <c r="G32" s="8" t="s">
+      <c r="C44" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D44" t="s">
+        <v>220</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.84722222222222221</v>
+      </c>
+      <c r="F44" s="8">
+        <v>235202</v>
+      </c>
+      <c r="G44" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H44" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I32" s="8">
-        <v>53104</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N32" t="s">
-        <v>194</v>
-      </c>
-      <c r="O32" t="s">
-        <v>194</v>
-      </c>
-      <c r="P32">
+      <c r="I44" s="8">
+        <v>53116</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="26">
+        <v>5</v>
+      </c>
+      <c r="N44" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="30" t="s">
+      <c r="R44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R32" s="30" t="s">
+      <c r="T44" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S32">
-        <v>3.35</v>
-      </c>
-      <c r="T32">
-        <v>63.9</v>
-      </c>
-      <c r="U32">
-        <v>42.3</v>
-      </c>
-      <c r="V32">
-        <v>98</v>
-      </c>
-      <c r="W32" t="s">
+      <c r="U44">
+        <v>2.9</v>
+      </c>
+      <c r="V44">
+        <v>63.1</v>
+      </c>
+      <c r="W44">
+        <v>49.4</v>
+      </c>
+      <c r="X44">
+        <v>97.6</v>
+      </c>
+      <c r="Y44" t="s">
         <v>17</v>
       </c>
-      <c r="X32" t="s">
+      <c r="Z44" t="s">
         <v>126</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="AA44" t="s">
         <v>195</v>
       </c>
-      <c r="AA32">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="AD32" t="s">
+      <c r="AC44">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="s">
         <v>21</v>
       </c>
-      <c r="AE32">
-        <v>1</v>
-      </c>
-      <c r="AF32">
-        <v>1</v>
-      </c>
-      <c r="AG32">
-        <v>1</v>
-      </c>
-      <c r="AH32">
-        <v>1</v>
-      </c>
-      <c r="AI32">
-        <v>1</v>
-      </c>
-      <c r="AJ32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="AG44">
+        <v>1</v>
+      </c>
+      <c r="AH44">
+        <v>1</v>
+      </c>
+      <c r="AI44">
+        <v>1</v>
+      </c>
+      <c r="AJ44">
+        <v>1</v>
+      </c>
+      <c r="AK44">
+        <v>1</v>
+      </c>
+      <c r="AL44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>12</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B45" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="4">
-        <v>45160</v>
-      </c>
-      <c r="D33" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0.84930555555555554</v>
-      </c>
-      <c r="F33" s="8">
-        <v>235191</v>
-      </c>
-      <c r="G33" s="8" t="s">
+      <c r="C45" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D45" t="s">
+        <v>221</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.87708333333333333</v>
+      </c>
+      <c r="F45" s="8">
+        <v>235203</v>
+      </c>
+      <c r="G45" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H45" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I33" s="8">
-        <v>53105</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L33" s="8" t="s">
+      <c r="I45" s="8">
+        <v>53117</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="N33" t="s">
-        <v>194</v>
-      </c>
-      <c r="O33" t="s">
-        <v>194</v>
-      </c>
-      <c r="P33">
+      <c r="M45" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P45" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S45" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="T45" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="U45">
+        <v>2.9</v>
+      </c>
+      <c r="V45">
+        <v>62.1</v>
+      </c>
+      <c r="W45">
+        <v>50</v>
+      </c>
+      <c r="X45">
+        <v>96.4</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC45">
+        <v>1</v>
+      </c>
+      <c r="AE45" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG45">
+        <v>1</v>
+      </c>
+      <c r="AH45">
+        <v>1</v>
+      </c>
+      <c r="AI45">
+        <v>1</v>
+      </c>
+      <c r="AJ45">
+        <v>1</v>
+      </c>
+      <c r="AK45">
+        <v>1</v>
+      </c>
+      <c r="AL45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="4">
+        <v>45161</v>
+      </c>
+      <c r="D46" t="s">
+        <v>222</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0.90555555555555556</v>
+      </c>
+      <c r="F46" s="8">
+        <v>235204</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I46" s="8">
+        <v>53118</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N46" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="30" t="s">
+      <c r="R46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="R33" s="30" t="s">
+      <c r="T46" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S33">
-        <v>3.45</v>
-      </c>
-      <c r="T33">
-        <v>63.1</v>
-      </c>
-      <c r="U33">
-        <v>39.4</v>
-      </c>
-      <c r="V33">
-        <v>97.7</v>
-      </c>
-      <c r="W33" t="s">
+      <c r="U46">
+        <v>2.5</v>
+      </c>
+      <c r="V46">
+        <v>62.2</v>
+      </c>
+      <c r="W46">
+        <v>48.5</v>
+      </c>
+      <c r="X46">
+        <v>97.5</v>
+      </c>
+      <c r="Y46" t="s">
         <v>17</v>
       </c>
-      <c r="X33" t="s">
+      <c r="Z46" t="s">
         <v>126</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="AA46" t="s">
         <v>195</v>
       </c>
-      <c r="AA33">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="AD33" t="s">
+      <c r="AC46">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="s">
         <v>21</v>
       </c>
-      <c r="AE33">
-        <v>1</v>
-      </c>
-      <c r="AF33">
-        <v>1</v>
-      </c>
-      <c r="AG33">
-        <v>1</v>
-      </c>
-      <c r="AH33">
-        <v>1</v>
-      </c>
-      <c r="AI33">
-        <v>1</v>
-      </c>
-      <c r="AJ33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="4">
-        <v>45160</v>
-      </c>
-      <c r="D34" t="s">
-        <v>189</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0.89027777777777783</v>
-      </c>
-      <c r="F34" s="8">
-        <v>235192</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I34" s="8">
-        <v>53106</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N34" t="s">
-        <v>194</v>
-      </c>
-      <c r="O34" t="s">
-        <v>194</v>
-      </c>
-      <c r="P34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R34" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S34">
-        <v>3.35</v>
-      </c>
-      <c r="T34">
-        <v>66.8</v>
-      </c>
-      <c r="U34">
-        <v>42.5</v>
-      </c>
-      <c r="V34">
-        <v>95.9</v>
-      </c>
-      <c r="W34" t="s">
-        <v>17</v>
-      </c>
-      <c r="X34" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA34">
-        <v>1</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE34">
-        <v>1</v>
-      </c>
-      <c r="AF34">
-        <v>1</v>
-      </c>
-      <c r="AG34">
-        <v>1</v>
-      </c>
-      <c r="AH34">
-        <v>1</v>
-      </c>
-      <c r="AI34">
-        <v>1</v>
-      </c>
-      <c r="AJ34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D35" t="s">
-        <v>202</v>
-      </c>
-      <c r="E35" s="5">
-        <v>0.38472222222222219</v>
-      </c>
-      <c r="F35" s="8">
-        <v>235193</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I35" s="8">
-        <v>53107</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="O35" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="P35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R35" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S35">
-        <v>3.7</v>
-      </c>
-      <c r="T35">
-        <v>66.3</v>
-      </c>
-      <c r="U35">
-        <v>44.3</v>
-      </c>
-      <c r="V35">
-        <v>99.3</v>
-      </c>
-      <c r="W35" t="s">
-        <v>17</v>
-      </c>
-      <c r="X35" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA35">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE35">
-        <v>1</v>
-      </c>
-      <c r="AF35">
-        <v>1</v>
-      </c>
-      <c r="AG35">
-        <v>1</v>
-      </c>
-      <c r="AH35">
-        <v>1</v>
-      </c>
-      <c r="AI35">
-        <v>1</v>
-      </c>
-      <c r="AJ35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D36" t="s">
-        <v>203</v>
-      </c>
-      <c r="E36" s="5">
-        <v>0.42152777777777778</v>
-      </c>
-      <c r="F36" s="8">
-        <v>235194</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I36" s="8">
-        <v>53108</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="O36" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="P36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R36" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S36">
-        <v>3.25</v>
-      </c>
-      <c r="T36">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="U36">
-        <v>44.1</v>
-      </c>
-      <c r="V36">
-        <v>100.1</v>
-      </c>
-      <c r="W36" t="s">
-        <v>17</v>
-      </c>
-      <c r="X36" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA36">
-        <v>1</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE36">
-        <v>1</v>
-      </c>
-      <c r="AF36">
-        <v>1</v>
-      </c>
-      <c r="AG36">
-        <v>1</v>
-      </c>
-      <c r="AH36">
-        <v>1</v>
-      </c>
-      <c r="AI36">
-        <v>1</v>
-      </c>
-      <c r="AJ36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:36" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D37" t="s">
-        <v>204</v>
-      </c>
-      <c r="E37" s="5">
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="F37" s="8">
-        <v>235195</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I37" s="8">
-        <v>53109</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M37" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P37">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q37" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="R37" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="S37">
-        <v>3.35</v>
-      </c>
-      <c r="T37">
-        <v>66.7</v>
-      </c>
-      <c r="U37">
-        <v>49.6</v>
-      </c>
-      <c r="V37">
-        <v>99.9</v>
-      </c>
-      <c r="W37" t="s">
-        <v>17</v>
-      </c>
-      <c r="X37" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA37">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>213</v>
-      </c>
-      <c r="AE37">
-        <v>1</v>
-      </c>
-      <c r="AF37">
-        <v>1</v>
-      </c>
-      <c r="AG37">
-        <v>1</v>
-      </c>
-      <c r="AH37">
-        <v>1</v>
-      </c>
-      <c r="AI37">
-        <v>1</v>
-      </c>
-      <c r="AJ37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D38" t="s">
-        <v>205</v>
-      </c>
-      <c r="E38" s="5">
-        <v>0.50347222222222221</v>
-      </c>
-      <c r="F38" s="8">
-        <v>235196</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I38" s="8">
-        <v>53110</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="O38" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="P38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R38" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S38">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="T38">
-        <v>63.6</v>
-      </c>
-      <c r="U38">
-        <v>41.7</v>
-      </c>
-      <c r="V38">
-        <v>98.1</v>
-      </c>
-      <c r="W38" t="s">
-        <v>17</v>
-      </c>
-      <c r="X38" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA38">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE38">
-        <v>1</v>
-      </c>
-      <c r="AF38">
-        <v>1</v>
-      </c>
-      <c r="AG38">
-        <v>1</v>
-      </c>
-      <c r="AH38">
-        <v>1</v>
-      </c>
-      <c r="AI38">
-        <v>1</v>
-      </c>
-      <c r="AJ38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D39" t="s">
-        <v>206</v>
-      </c>
-      <c r="E39" s="5">
-        <v>0.5444444444444444</v>
-      </c>
-      <c r="F39" s="8">
-        <v>235197</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I39" s="8">
-        <v>53111</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M39" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O39" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R39" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S39">
-        <v>2.95</v>
-      </c>
-      <c r="T39">
-        <v>62.9</v>
-      </c>
-      <c r="U39">
-        <v>49.4</v>
-      </c>
-      <c r="V39">
-        <v>100</v>
-      </c>
-      <c r="W39" t="s">
-        <v>17</v>
-      </c>
-      <c r="X39" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA39">
-        <v>1</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>213</v>
-      </c>
-      <c r="AE39">
-        <v>1</v>
-      </c>
-      <c r="AF39">
-        <v>1</v>
-      </c>
-      <c r="AG39">
-        <v>1</v>
-      </c>
-      <c r="AH39">
-        <v>1</v>
-      </c>
-      <c r="AI39">
-        <v>1</v>
-      </c>
-      <c r="AJ39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D40" t="s">
-        <v>207</v>
-      </c>
-      <c r="E40" s="5">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="F40" s="8">
-        <v>235198</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I40" s="8">
-        <v>53112</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="P40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R40" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S40">
-        <v>3.55</v>
-      </c>
-      <c r="T40">
-        <v>66.8</v>
-      </c>
-      <c r="U40">
-        <v>43.6</v>
-      </c>
-      <c r="V40">
-        <v>97.2</v>
-      </c>
-      <c r="W40" t="s">
-        <v>17</v>
-      </c>
-      <c r="X40" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA40">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE40">
-        <v>1</v>
-      </c>
-      <c r="AF40">
-        <v>1</v>
-      </c>
-      <c r="AG40">
-        <v>1</v>
-      </c>
-      <c r="AH40">
-        <v>1</v>
-      </c>
-      <c r="AI40">
-        <v>1</v>
-      </c>
-      <c r="AJ40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D41" t="s">
-        <v>208</v>
-      </c>
-      <c r="E41" s="5">
-        <v>0.68194444444444446</v>
-      </c>
-      <c r="F41" s="8">
-        <v>235199</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I41" s="8">
-        <v>53113</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O41" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="P41">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q41" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="R41" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="S41">
-        <v>2.6</v>
-      </c>
-      <c r="T41">
-        <v>63.2</v>
-      </c>
-      <c r="U41">
-        <v>50.3</v>
-      </c>
-      <c r="V41">
-        <v>100.4</v>
-      </c>
-      <c r="W41" t="s">
-        <v>17</v>
-      </c>
-      <c r="X41" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA41">
-        <v>1</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>213</v>
-      </c>
-      <c r="AE41">
-        <v>1</v>
-      </c>
-      <c r="AF41">
-        <v>1</v>
-      </c>
-      <c r="AG41">
-        <v>1</v>
-      </c>
-      <c r="AH41">
-        <v>1</v>
-      </c>
-      <c r="AI41">
-        <v>1</v>
-      </c>
-      <c r="AJ41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D42" t="s">
-        <v>209</v>
-      </c>
-      <c r="E42" s="5">
-        <v>0.78125</v>
-      </c>
-      <c r="F42" s="8">
-        <v>235200</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I42" s="8">
-        <v>53114</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" s="26">
-        <v>6</v>
-      </c>
-      <c r="N42" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O42" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P42">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q42" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="R42" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="S42">
-        <v>3.4</v>
-      </c>
-      <c r="T42">
-        <v>64.8</v>
-      </c>
-      <c r="U42">
-        <v>50.4</v>
-      </c>
-      <c r="V42">
-        <v>98.1</v>
-      </c>
-      <c r="W42" t="s">
-        <v>17</v>
-      </c>
-      <c r="X42" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA42">
-        <v>1</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE42">
-        <v>1</v>
-      </c>
-      <c r="AF42">
-        <v>1</v>
-      </c>
-      <c r="AG42">
-        <v>1</v>
-      </c>
-      <c r="AH42">
-        <v>1</v>
-      </c>
-      <c r="AI42">
-        <v>1</v>
-      </c>
-      <c r="AJ42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D43" t="s">
-        <v>219</v>
-      </c>
-      <c r="E43" s="5">
-        <v>0.80902777777777779</v>
-      </c>
-      <c r="F43" s="8">
-        <v>235201</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I43" s="8">
-        <v>53115</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R43" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S43">
-        <v>2.8</v>
-      </c>
-      <c r="T43">
-        <v>64.7</v>
-      </c>
-      <c r="U43">
-        <v>50.2</v>
-      </c>
-      <c r="V43">
-        <v>100.5</v>
-      </c>
-      <c r="W43" t="s">
-        <v>17</v>
-      </c>
-      <c r="X43" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA43">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE43">
-        <v>1</v>
-      </c>
-      <c r="AF43">
-        <v>1</v>
-      </c>
-      <c r="AG43">
-        <v>1</v>
-      </c>
-      <c r="AH43">
-        <v>1</v>
-      </c>
-      <c r="AI43">
-        <v>1</v>
-      </c>
-      <c r="AJ43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D44" t="s">
-        <v>220</v>
-      </c>
-      <c r="E44" s="5">
-        <v>0.84722222222222221</v>
-      </c>
-      <c r="F44" s="8">
-        <v>235202</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I44" s="8">
-        <v>53116</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" s="26">
-        <v>5</v>
-      </c>
-      <c r="N44" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O44" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R44" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S44">
-        <v>2.9</v>
-      </c>
-      <c r="T44">
-        <v>63.1</v>
-      </c>
-      <c r="U44">
-        <v>49.4</v>
-      </c>
-      <c r="V44">
-        <v>97.6</v>
-      </c>
-      <c r="W44" t="s">
-        <v>17</v>
-      </c>
-      <c r="X44" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA44">
-        <v>1</v>
-      </c>
-      <c r="AD44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE44">
-        <v>1</v>
-      </c>
-      <c r="AF44">
-        <v>1</v>
-      </c>
-      <c r="AG44">
-        <v>1</v>
-      </c>
-      <c r="AH44">
-        <v>1</v>
-      </c>
-      <c r="AI44">
-        <v>1</v>
-      </c>
-      <c r="AJ44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D45" t="s">
-        <v>221</v>
-      </c>
-      <c r="E45" s="5">
-        <v>0.87708333333333333</v>
-      </c>
-      <c r="F45" s="8">
-        <v>235203</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I45" s="8">
-        <v>53117</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L45" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M45" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="N45" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O45" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="P45">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q45" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="R45" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="S45">
-        <v>2.9</v>
-      </c>
-      <c r="T45">
-        <v>62.1</v>
-      </c>
-      <c r="U45">
-        <v>50</v>
-      </c>
-      <c r="V45">
-        <v>96.4</v>
-      </c>
-      <c r="W45" t="s">
-        <v>17</v>
-      </c>
-      <c r="X45" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA45">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AD45" t="s">
-        <v>213</v>
-      </c>
-      <c r="AE45">
-        <v>1</v>
-      </c>
-      <c r="AF45">
-        <v>1</v>
-      </c>
-      <c r="AG45">
-        <v>1</v>
-      </c>
-      <c r="AH45">
-        <v>1</v>
-      </c>
-      <c r="AI45">
-        <v>1</v>
-      </c>
-      <c r="AJ45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="4">
-        <v>45161</v>
-      </c>
-      <c r="D46" t="s">
-        <v>222</v>
-      </c>
-      <c r="E46" s="5">
-        <v>0.90555555555555556</v>
-      </c>
-      <c r="F46" s="8">
-        <v>235204</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I46" s="8">
-        <v>53118</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L46" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M46" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="N46" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O46" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R46" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="S46">
-        <v>2.5</v>
-      </c>
-      <c r="T46">
-        <v>62.2</v>
-      </c>
-      <c r="U46">
-        <v>48.5</v>
-      </c>
-      <c r="V46">
-        <v>97.5</v>
-      </c>
-      <c r="W46" t="s">
-        <v>17</v>
-      </c>
-      <c r="X46" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA46">
-        <v>1</v>
-      </c>
-      <c r="AD46" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE46">
-        <v>1</v>
-      </c>
-      <c r="AF46">
-        <v>1</v>
-      </c>
       <c r="AG46">
         <v>1</v>
       </c>
@@ -6699,8 +6978,14 @@
       <c r="AJ46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK46">
+        <v>1</v>
+      </c>
+      <c r="AL46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -6746,52 +7031,53 @@
       <c r="O47" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q47">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q47" s="30" t="s">
+      <c r="R47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S47" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R47" s="30" t="s">
+      <c r="T47" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S47">
+      <c r="U47">
         <v>2.75</v>
       </c>
-      <c r="T47">
+      <c r="V47">
         <v>58.4</v>
       </c>
-      <c r="U47">
+      <c r="W47">
         <v>49.8</v>
       </c>
-      <c r="V47">
+      <c r="X47">
         <v>106.6</v>
       </c>
-      <c r="W47" t="s">
+      <c r="Y47" t="s">
         <v>17</v>
       </c>
-      <c r="X47" t="s">
+      <c r="Z47" t="s">
         <v>126</v>
       </c>
-      <c r="Y47" t="s">
+      <c r="AA47" t="s">
         <v>195</v>
       </c>
-      <c r="AA47">
-        <v>1</v>
-      </c>
-      <c r="AC47" s="19" t="s">
+      <c r="AC47">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="AD47" t="s">
+      <c r="AF47" t="s">
         <v>21</v>
       </c>
-      <c r="AE47">
-        <v>1</v>
-      </c>
-      <c r="AF47">
-        <v>1</v>
-      </c>
       <c r="AG47">
         <v>1</v>
       </c>
@@ -6804,8 +7090,14 @@
       <c r="AJ47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK47">
+        <v>1</v>
+      </c>
+      <c r="AL47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -6851,52 +7143,53 @@
       <c r="O48" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q48">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q48" s="30" t="s">
+      <c r="R48">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S48" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R48" s="30" t="s">
+      <c r="T48" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="S48">
+      <c r="U48">
         <v>2.5499999999999998</v>
       </c>
-      <c r="T48">
+      <c r="V48">
         <v>60.7</v>
       </c>
-      <c r="U48">
+      <c r="W48">
         <v>47.9</v>
       </c>
-      <c r="V48">
+      <c r="X48">
         <v>95</v>
       </c>
-      <c r="W48" t="s">
+      <c r="Y48" t="s">
         <v>17</v>
       </c>
-      <c r="X48" t="s">
+      <c r="Z48" t="s">
         <v>126</v>
       </c>
-      <c r="Y48" t="s">
+      <c r="AA48" t="s">
         <v>195</v>
       </c>
-      <c r="AA48">
-        <v>1</v>
-      </c>
-      <c r="AC48" s="19" t="s">
+      <c r="AC48">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="AD48" t="s">
+      <c r="AF48" t="s">
         <v>213</v>
       </c>
-      <c r="AE48">
-        <v>1</v>
-      </c>
-      <c r="AF48">
-        <v>1</v>
-      </c>
       <c r="AG48">
         <v>1</v>
       </c>
@@ -6907,6 +7200,12 @@
         <v>1</v>
       </c>
       <c r="AJ48">
+        <v>1</v>
+      </c>
+      <c r="AK48">
+        <v>1</v>
+      </c>
+      <c r="AL48">
         <v>1</v>
       </c>
     </row>
@@ -6914,6 +7213,43 @@
       <c r="M1048576" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL48" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="201284"/>
+        <filter val="222289"/>
+        <filter val="222450"/>
+        <filter val="233658"/>
+        <filter val="233659"/>
+        <filter val="233660"/>
+        <filter val="233661"/>
+        <filter val="233662"/>
+        <filter val="233663"/>
+        <filter val="233664"/>
+        <filter val="233665"/>
+        <filter val="233666"/>
+        <filter val="233667"/>
+        <filter val="233668"/>
+        <filter val="233669"/>
+        <filter val="233670"/>
+        <filter val="233671"/>
+        <filter val="233672"/>
+        <filter val="235195"/>
+        <filter val="235197"/>
+        <filter val="235199"/>
+        <filter val="235200"/>
+        <filter val="235201"/>
+        <filter val="235202"/>
+        <filter val="235203"/>
+        <filter val="235204"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="adult"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
